--- a/VisualStudioNumPadTemplate.xlsx
+++ b/VisualStudioNumPadTemplate.xlsx
@@ -70,15 +70,9 @@
     <t>Merge</t>
   </si>
   <si>
-    <t>(Fetch)</t>
-  </si>
-  <si>
     <t>CoPilot</t>
   </si>
   <si>
-    <t>A+] or [</t>
-  </si>
-  <si>
     <t>Alt Suggestions</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
     <t>Trigger On</t>
   </si>
   <si>
-    <t>C+A+</t>
-  </si>
-  <si>
     <t>Open Copilot</t>
   </si>
   <si>
@@ -107,13 +98,22 @@
   </si>
   <si>
     <t>View Branches</t>
+  </si>
+  <si>
+    <t>A+, or .</t>
+  </si>
+  <si>
+    <t>C+A+ENTR</t>
+  </si>
+  <si>
+    <t>A+/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +142,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -163,7 +170,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -350,13 +357,52 @@
         <color indexed="64"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -364,18 +410,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -412,29 +446,48 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -799,69 +852,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25"/>
-      <c r="B1" s="26"/>
-      <c r="C1" s="27"/>
+      <c r="A1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
+      <c r="A2" s="9">
         <v>7</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="10">
         <v>8</v>
       </c>
-      <c r="C2" s="15">
+      <c r="C2" s="11">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="17" t="s">
+      <c r="A4" s="31"/>
+      <c r="B4" s="32"/>
+      <c r="C4" s="13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="4">
         <v>5</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="14">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="33" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="20"/>
+      <c r="C7" s="34"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -870,83 +923,103 @@
       <c r="B8" s="2">
         <v>2</v>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="15">
         <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="30"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
+      <c r="B11" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="23"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="21"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="21"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C14" s="21"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="21"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="21"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B15:C15"/>
+  </mergeCells>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/VisualStudioNumPadTemplate.xlsx
+++ b/VisualStudioNumPadTemplate.xlsx
@@ -135,14 +135,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -452,12 +452,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -488,6 +483,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -868,10 +868,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -879,8 +879,8 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
       <c r="C4" s="13" t="s">
         <v>7</v>
       </c>
@@ -903,7 +903,7 @@
       <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="28" t="s">
         <v>2</v>
       </c>
     </row>
@@ -914,7 +914,7 @@
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="29"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -928,97 +928,97 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="22" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="24" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="25"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="23"/>
+      <c r="C11" s="32"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="21"/>
+      <c r="C12" s="33"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="21"/>
+      <c r="C13" s="33"/>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="21"/>
+      <c r="C14" s="33"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="21"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="33"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="A16" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="21"/>
+      <c r="C16" s="33"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="A17" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="21"/>
+      <c r="C17" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B16:C16"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/VisualStudioNumPadTemplate.xlsx
+++ b/VisualStudioNumPadTemplate.xlsx
@@ -453,41 +453,41 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -868,10 +868,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="27" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -879,8 +879,8 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
+      <c r="A4" s="31"/>
+      <c r="B4" s="32"/>
       <c r="C4" s="13" t="s">
         <v>7</v>
       </c>
@@ -903,7 +903,7 @@
       <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="33" t="s">
         <v>2</v>
       </c>
     </row>
@@ -914,7 +914,7 @@
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="29"/>
+      <c r="C7" s="34"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -928,97 +928,97 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="29" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="25"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="30"/>
+    </row>
+    <row r="11" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="32"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="24"/>
+    </row>
+    <row r="12" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="33"/>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="21"/>
+    </row>
+    <row r="13" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="33"/>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="21"/>
+    </row>
+    <row r="14" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="33"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="C14" s="21"/>
+    </row>
+    <row r="15" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="34"/>
-      <c r="C15" s="33"/>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="22"/>
+      <c r="C15" s="21"/>
+    </row>
+    <row r="16" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="33"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="21"/>
+    </row>
+    <row r="17" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="33" t="s">
+      <c r="B17" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="33"/>
+      <c r="C17" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C6:C7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/VisualStudioNumPadTemplate.xlsx
+++ b/VisualStudioNumPadTemplate.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Vw Hstry</t>
   </si>
@@ -73,18 +73,6 @@
     <t>CoPilot</t>
   </si>
   <si>
-    <t>Alt Suggestions</t>
-  </si>
-  <si>
-    <t>C+A+\</t>
-  </si>
-  <si>
-    <t>Trigger On</t>
-  </si>
-  <si>
-    <t>Open Copilot</t>
-  </si>
-  <si>
     <t>Git</t>
   </si>
   <si>
@@ -100,13 +88,19 @@
     <t>View Branches</t>
   </si>
   <si>
-    <t>A+, or .</t>
-  </si>
-  <si>
-    <t>C+A+ENTR</t>
-  </si>
-  <si>
     <t>A+/</t>
+  </si>
+  <si>
+    <t>A + /</t>
+  </si>
+  <si>
+    <t>Inline</t>
+  </si>
+  <si>
+    <t>C+\, C</t>
+  </si>
+  <si>
+    <t>Chat</t>
   </si>
 </sst>
 </file>
@@ -454,19 +448,30 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -476,18 +481,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -868,10 +862,10 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="23" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -879,8 +873,8 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="31"/>
-      <c r="B4" s="32"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="13" t="s">
         <v>7</v>
       </c>
@@ -903,7 +897,7 @@
       <c r="B6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="25" t="s">
         <v>2</v>
       </c>
     </row>
@@ -914,7 +908,7 @@
       <c r="B7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="34"/>
+      <c r="C7" s="26"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -928,84 +922,85 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="32" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="33"/>
     </row>
     <row r="11" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="24"/>
+      <c r="B11" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="28"/>
     </row>
     <row r="12" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="21"/>
+        <v>18</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="29"/>
     </row>
     <row r="13" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="21"/>
+        <v>20</v>
+      </c>
+      <c r="B13" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="29"/>
     </row>
     <row r="14" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="21"/>
+      <c r="A14" s="19"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="29"/>
     </row>
     <row r="15" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="21"/>
+        <v>12</v>
+      </c>
+      <c r="B15" s="34"/>
+      <c r="C15" s="29"/>
     </row>
     <row r="16" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="21"/>
+        <v>13</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="29"/>
     </row>
     <row r="17" spans="1:3" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="21"/>
+        <v>14</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C6:C7"/>
@@ -1014,11 +1009,6 @@
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="B9:B10"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.25" right="0" top="0.25" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
